--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -4119,38 +4119,30 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>14310400</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>25600</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K55" s="5" t="n">
+        <v>14310400</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>25600</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4159,7 +4151,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32432,7 +32424,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -32442,7 +32434,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>177</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32980,12 +32972,12 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
-招标单位
--
-(在售)</t>
+$1431万
+$25,600/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2451,38 +2451,30 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>17373200</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>25700</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K29" s="5" t="n">
+        <v>17373200</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>25700</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2483,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2712,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2777,38 +2769,30 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>17305600</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>25600</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K34" s="5" t="n">
+        <v>17305600</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>25600</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2817,7 +2801,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3922,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4000,7 +3984,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4248,7 +4232,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4930,7 +4914,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5178,7 +5162,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5240,7 +5224,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5364,7 +5348,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -6170,7 +6154,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6232,7 +6216,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6418,7 +6402,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6542,7 +6526,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6728,7 +6712,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7472,7 +7456,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7534,7 +7518,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7658,7 +7642,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8650,7 +8634,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8960,7 +8944,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9890,7 +9874,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -11130,7 +11114,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11440,7 +11424,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11688,7 +11672,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12060,7 +12044,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12308,7 +12292,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12618,7 +12602,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12928,7 +12912,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -15642,7 +15626,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15704,7 +15688,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -17626,7 +17610,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17812,7 +17796,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -19610,7 +19594,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19672,7 +19656,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19796,7 +19780,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -21594,7 +21578,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21656,7 +21640,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21780,7 +21764,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -23454,7 +23438,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23640,7 +23624,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -25438,7 +25422,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -27422,7 +27406,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27546,7 +27530,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27608,7 +27592,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27732,7 +27716,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -29406,7 +29390,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -29530,7 +29514,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -29592,7 +29576,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -30894,7 +30878,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -31018,7 +31002,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -31204,7 +31188,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -31390,7 +31374,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -31514,7 +31498,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -31576,7 +31560,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -31700,7 +31684,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -32424,7 +32408,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -32434,7 +32418,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>179</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32745,12 +32729,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
+$1737万
+$25,700/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -32758,7 +32742,7 @@
           <t>E | 423呎 (2房)
 $960万
 $22,683/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -32792,12 +32776,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
+$1731万
+$25,600/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -32805,7 +32789,7 @@
           <t>E | 423呎 (2房)
 $950万
 $22,459/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -32914,7 +32898,7 @@
           <t>A | 655呎 (3房)
 $1371万
 $20,931/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -32961,7 +32945,7 @@
           <t>A | 655呎 (3房)
 $1363万
 $20,806/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -32993,7 +32977,7 @@
           <t>E | 423呎 (2房)
 $920万
 $21,754/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -33102,7 +33086,7 @@
           <t>A | 655呎 (3房)
 $1230万
 $18,774/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -33134,7 +33118,7 @@
           <t>E | 423呎 (2房)
 $825万
 $19,511/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -33165,7 +33149,7 @@
           <t>C | 559呎 (3房)
 $1415万
 $25,313/呎
-(26年-08月-23日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -33181,7 +33165,7 @@
           <t>E | 423呎 (2房)
 $820万
 $19,395/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -33290,7 +33274,7 @@
           <t>A | 655呎 (3房)
 $1215万
 $18,551/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -33314,10 +33298,57 @@
           <t>D | 676呎 (3房)
 $1616万
 $23,901/呎
-(26年-08月-23日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 423呎 (2房)
+$806万
+$19,050/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 655呎 (3房)
+$1331万
+$20,318/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 444呎 (2房)
+$833万
+$18,770/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 559呎 (3房)
+$1477万
+$26,415/呎
+(26年-09月-05日)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 676呎 (3房)
+$1614万
+$23,880/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
 $806万
@@ -33326,53 +33357,6 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 655呎 (3房)
-$1331万
-$20,318/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 444呎 (2房)
-$833万
-$18,770/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 559呎 (3房)
-$1477万
-$26,415/呎
-(26年-09月-05日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 676呎 (3房)
-$1614万
-$23,880/呎
-(26年-08月-23日)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 423呎 (2房)
-$806万
-$19,050/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-    </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
@@ -33478,7 +33462,7 @@
           <t>A | 657呎 (3房)
 $1183万
 $18,003/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -33494,7 +33478,7 @@
           <t>C | 558呎 (3房)
 $1436万
 $25,738/呎
-(26年-08月-23日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -33502,7 +33486,7 @@
           <t>D | 680呎 (3房)
 $1564万
 $23,000/呎
-(26年-08月-23日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -33698,7 +33682,7 @@
           <t>E | 422呎 (2房)
 $762万
 $18,045/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -33745,7 +33729,7 @@
           <t>E | 422呎 (2房)
 $762万
 $18,045/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -33886,7 +33870,7 @@
           <t>E | 422呎 (2房)
 $815万
 $19,313/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -34074,7 +34058,7 @@
           <t>E | 422呎 (2房)
 $705万
 $16,716/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -34089,7 +34073,7 @@
           <t>A | 657呎 (3房)
 $1280万
 $19,481/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -34121,7 +34105,7 @@
           <t>E | 422呎 (2房)
 $782万
 $18,528/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -34183,7 +34167,7 @@
           <t>A | 657呎 (3房)
 $1272万
 $19,364/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -34215,7 +34199,7 @@
           <t>E | 422呎 (2房)
 $733万
 $17,365/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34214,7 @@
           <t>A | 657呎 (3房)
 $1188万
 $18,088/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -34277,7 +34261,7 @@
           <t>A | 619呎 (3房)
 $1486万
 $24,000/呎
-(26年-08月-23日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -34858,7 +34842,7 @@
           <t>E | 418呎 (2房)
 $853万
 $20,397/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34866,7 +34850,7 @@
           <t>F | 450呎 (2房)
 $924万
 $20,531/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -35126,7 +35110,7 @@
           <t>C | 306呎 (1房)
 $596万
 $19,480/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -35150,7 +35134,7 @@
           <t>F | 450呎 (2房)
 $982万
 $21,824/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -35410,7 +35394,7 @@
           <t>C | 306呎 (1房)
 $587万
 $19,176/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -35426,7 +35410,7 @@
           <t>E | 418呎 (2房)
 $760万
 $18,182/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -35434,7 +35418,7 @@
           <t>F | 450呎 (2房)
 $870万
 $19,342/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -35694,7 +35678,7 @@
           <t>C | 306呎 (1房)
 $580万
 $18,948/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -35710,10 +35694,81 @@
           <t>E | 418呎 (2房)
 $751万
 $17,967/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 450呎 (2房)
+$851万
+$18,909/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
+$870万
+$21,311/呎
+(26年-09月-05日)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 473呎 (2房)
+$903万
+$19,087/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 672呎 (3房)
+$1448万
+$21,546/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 313呎 (1房)
+$590万
+$18,847/呎
+(26年-09月-05日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 306呎 (1房)
+$580万
+$18,948/呎
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$629万
+$20,495/呎
+(26年-09月-05日)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 418呎 (2房)
+$769万
+$18,395/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 450呎 (2房)
 $851万
@@ -35721,7 +35776,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $870万
@@ -35729,77 +35784,6 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>H | 473呎 (2房)
-$903万
-$19,087/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 672呎 (3房)
-$1448万
-$21,546/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 313呎 (1房)
-$590万
-$18,847/呎
-(26年-09月-05日)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 306呎 (1房)
-$580万
-$18,948/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$629万
-$20,495/呎
-(26年-09月-05日)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 418呎 (2房)
-$769万
-$18,395/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>F | 450呎 (2房)
-$851万
-$18,909/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
-$870万
-$21,311/呎
-(26年-09月-05日)</t>
-        </is>
-      </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 473呎 (2房)
@@ -35994,7 +35978,7 @@
           <t>E | 422呎 (2房)
 $745万
 $17,645/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -36018,7 +36002,7 @@
           <t>H | 476呎 (2房)
 $871万
 $18,298/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -36302,7 +36286,7 @@
           <t>H | 476呎 (2房)
 $942万
 $19,800/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -36546,7 +36530,7 @@
           <t>C | 304呎 (1房)
 $545万
 $17,931/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -36562,7 +36546,7 @@
           <t>E | 422呎 (2房)
 $733万
 $17,365/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -36570,7 +36554,7 @@
           <t>F | 448呎 (2房)
 $868万
 $19,382/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -36586,7 +36570,7 @@
           <t>H | 476呎 (2房)
 $931万
 $19,565/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -36846,7 +36830,7 @@
           <t>E | 422呎 (2房)
 $796万
 $18,865/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -36854,7 +36838,7 @@
           <t>F | 448呎 (2房)
 $743万
 $16,592/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H38" s="20" t="inlineStr">
@@ -36870,7 +36854,7 @@
           <t>H | 476呎 (2房)
 $875万
 $18,380/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -37043,7 +37027,7 @@
           <t>C | 304呎 (1房)
 $549万
 $18,066/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
@@ -37067,7 +37051,7 @@
           <t>F | 448呎 (2房)
 $737万
 $16,444/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H41" s="20" t="inlineStr">
@@ -37083,7 +37067,7 @@
           <t>H | 476呎 (2房)
 $800万
 $16,798/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -37114,7 +37098,7 @@
           <t>C | 304呎 (1房)
 $580万
 $19,089/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
@@ -37130,7 +37114,7 @@
           <t>E | 422呎 (2房)
 $699万
 $16,559/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
@@ -37138,7 +37122,7 @@
           <t>F | 448呎 (2房)
 $776万
 $17,326/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H42" s="20" t="inlineStr">
@@ -37154,7 +37138,7 @@
           <t>H | 476呎 (2房)
 $795万
 $16,697/呎
-(26年-08月-22日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20152,7 +20152,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25112,7 +25112,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25546,7 +25546,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25608,7 +25608,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -27096,7 +27096,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27902,7 +27902,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -28026,7 +28026,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -28088,7 +28088,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28212,7 +28212,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28398,7 +28398,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28522,7 +28522,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28584,7 +28584,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -29080,7 +29080,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -30010,7 +30010,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -30072,7 +30072,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -30506,7 +30506,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -32710,7 +32710,7 @@
           <t>A | 655呎 (3房)
 $1297万
 $19,808/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -32804,7 +32804,7 @@
           <t>A | 655呎 (3房)
 $1393万
 $21,267/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -32836,7 +32836,7 @@
           <t>E | 423呎 (2房)
 $859万
 $20,305/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -32930,7 +32930,7 @@
           <t>E | 423呎 (2房)
 $931万
 $22,017/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -33024,7 +33024,7 @@
           <t>E | 423呎 (2房)
 $915万
 $21,626/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -33110,7 +33110,7 @@
           <t>D | 676呎 (3房)
 $1683万
 $24,901/呎
-(26年-08月-23日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -33133,7 +33133,7 @@
           <t>A | 655呎 (3房)
 $1226万
 $18,718/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -33180,7 +33180,7 @@
           <t>A | 655呎 (3房)
 $1222万
 $18,663/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -33196,7 +33196,7 @@
           <t>C | 559呎 (3房)
 $1409万
 $25,200/呎
-(26年-08月-23日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -33204,7 +33204,7 @@
           <t>D | 676呎 (3房)
 $1670万
 $24,701/呎
-(26年-08月-23日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -33212,7 +33212,7 @@
           <t>E | 423呎 (2房)
 $816万
 $19,279/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -33368,7 +33368,7 @@
           <t>A | 655呎 (3房)
 $1194万
 $18,221/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -33384,7 +33384,7 @@
           <t>C | 559呎 (3房)
 $1342万
 $24,000/呎
-(26年-08月-23日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -33392,7 +33392,7 @@
           <t>D | 676呎 (3房)
 $1678万
 $24,830/呎
-(26年-08月-23日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -33494,7 +33494,7 @@
           <t>E | 422呎 (2房)
 $844万
 $20,002/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -33588,7 +33588,7 @@
           <t>E | 422呎 (2房)
 $766万
 $18,152/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -33650,7 +33650,7 @@
           <t>A | 657呎 (3房)
 $1301万
 $19,796/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -33744,7 +33744,7 @@
           <t>A | 657呎 (3房)
 $1169万
 $17,788/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -33776,7 +33776,7 @@
           <t>E | 422呎 (2房)
 $748万
 $17,723/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -33838,7 +33838,7 @@
           <t>A | 657呎 (3房)
 $1178万
 $17,930/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -33885,7 +33885,7 @@
           <t>A | 657呎 (3房)
 $1176万
 $17,893/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -33917,7 +33917,7 @@
           <t>E | 422呎 (2房)
 $820万
 $19,429/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -33932,7 +33932,7 @@
           <t>A | 657呎 (3房)
 $1159万
 $17,645/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -33964,7 +33964,7 @@
           <t>E | 422呎 (2房)
 $814万
 $19,294/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
           <t>E | 422呎 (2房)
 $802万
 $19,002/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -34026,7 +34026,7 @@
           <t>A | 657呎 (3房)
 $1169万
 $17,787/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -34120,7 +34120,7 @@
           <t>A | 657呎 (3房)
 $1164万
 $17,717/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -34152,7 +34152,7 @@
           <t>E | 422呎 (2房)
 $710万
 $16,815/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -34246,7 +34246,7 @@
           <t>E | 422呎 (2房)
 $770万
 $18,254/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -34700,7 +34700,7 @@
           <t>E | 418呎 (2房)
 $783万
 $18,734/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -34708,7 +34708,7 @@
           <t>F | 450呎 (2房)
 $942万
 $20,942/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -34968,7 +34968,7 @@
           <t>C | 306呎 (1房)
 $598万
 $19,539/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -34984,7 +34984,7 @@
           <t>E | 418呎 (2房)
 $848万
 $20,275/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -35055,7 +35055,7 @@
           <t>E | 418呎 (2房)
 $845万
 $20,215/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -35181,7 +35181,7 @@
           <t>C | 306呎 (1房)
 $607万
 $19,827/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -35268,7 +35268,7 @@
           <t>E | 418呎 (2房)
 $837万
 $20,033/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -35276,7 +35276,7 @@
           <t>F | 450呎 (2房)
 $965万
 $21,438/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -35465,7 +35465,7 @@
           <t>C | 306呎 (1房)
 $585万
 $19,118/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -35481,7 +35481,7 @@
           <t>E | 418呎 (2房)
 $758万
 $18,127/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -35489,7 +35489,7 @@
           <t>F | 450呎 (2房)
 $865万
 $19,227/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -35536,7 +35536,7 @@
           <t>C | 306呎 (1房)
 $639万
 $20,876/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -35552,7 +35552,7 @@
           <t>E | 418呎 (2房)
 $756万
 $18,074/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -35560,7 +35560,7 @@
           <t>F | 450呎 (2房)
 $860万
 $19,111/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -35623,7 +35623,7 @@
           <t>E | 418呎 (2房)
 $753万
 $18,019/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -35749,7 +35749,7 @@
           <t>C | 306呎 (1房)
 $580万
 $18,948/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -35765,7 +35765,7 @@
           <t>E | 418呎 (2房)
 $769万
 $18,395/呎
-(26年-08月-22日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -35773,7 +35773,7 @@
           <t>F | 450呎 (2房)
 $851万
 $18,909/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -35820,7 +35820,7 @@
           <t>C | 306呎 (1房)
 $590万
 $19,284/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -35836,7 +35836,7 @@
           <t>E | 418呎 (2房)
 $818万
 $19,560/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -35844,7 +35844,7 @@
           <t>F | 450呎 (2房)
 $841万
 $18,684/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -35915,7 +35915,7 @@
           <t>F | 448呎 (2房)
 $829万
 $18,496/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -35986,7 +35986,7 @@
           <t>F | 448呎 (2房)
 $812万
 $18,127/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -36049,7 +36049,7 @@
           <t>E | 422呎 (2房)
 $814万
 $19,287/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -36057,7 +36057,7 @@
           <t>F | 448呎 (2房)
 $887万
 $19,792/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -36073,7 +36073,7 @@
           <t>H | 476呎 (2房)
 $858万
 $18,025/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -36104,7 +36104,7 @@
           <t>C | 304呎 (1房)
 $588万
 $19,359/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -36120,7 +36120,7 @@
           <t>E | 422呎 (2房)
 $812万
 $19,246/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -36128,7 +36128,7 @@
           <t>F | 448呎 (2房)
 $884万
 $19,734/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -36144,7 +36144,7 @@
           <t>H | 476呎 (2房)
 $948万
 $19,920/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -36191,7 +36191,7 @@
           <t>E | 422呎 (2房)
 $740万
 $17,540/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -36199,7 +36199,7 @@
           <t>F | 448呎 (2房)
 $843万
 $18,819/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -36246,7 +36246,7 @@
           <t>C | 304呎 (1房)
 $612万
 $20,118/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -36262,7 +36262,7 @@
           <t>E | 422呎 (2房)
 $739万
 $17,505/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -36270,7 +36270,7 @@
           <t>F | 448呎 (2房)
 $879万
 $19,616/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -36404,7 +36404,7 @@
           <t>E | 422呎 (2房)
 $806万
 $19,095/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -36412,7 +36412,7 @@
           <t>F | 448呎 (2房)
 $874万
 $19,498/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -36475,7 +36475,7 @@
           <t>E | 422呎 (2房)
 $734万
 $17,400/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -36483,7 +36483,7 @@
           <t>F | 448呎 (2房)
 $795万
 $17,750/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -36499,7 +36499,7 @@
           <t>H | 476呎 (2房)
 $843万
 $17,704/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -36601,7 +36601,7 @@
           <t>C | 304呎 (1房)
 $550万
 $18,095/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -36617,7 +36617,7 @@
           <t>E | 422呎 (2房)
 $801万
 $18,981/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -36625,7 +36625,7 @@
           <t>F | 448呎 (2房)
 $789万
 $17,607/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -36641,7 +36641,7 @@
           <t>H | 476呎 (2房)
 $916万
 $19,254/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -36672,7 +36672,7 @@
           <t>C | 304呎 (1房)
 $548万
 $18,039/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -36688,7 +36688,7 @@
           <t>E | 422呎 (2房)
 $799万
 $18,941/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -36696,7 +36696,7 @@
           <t>F | 448呎 (2房)
 $783万
 $17,484/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr">
@@ -36712,7 +36712,7 @@
           <t>H | 476呎 (2房)
 $840万
 $17,649/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36759,7 @@
           <t>E | 422呎 (2房)
 $728万
 $17,261/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -36767,7 +36767,7 @@
           <t>F | 448呎 (2房)
 $772万
 $17,223/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
@@ -36901,7 +36901,7 @@
           <t>E | 422呎 (2房)
 $796万
 $18,865/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
@@ -36909,7 +36909,7 @@
           <t>F | 448呎 (2房)
 $752万
 $16,792/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="H39" s="20" t="inlineStr">
@@ -36925,7 +36925,7 @@
           <t>H | 476呎 (2房)
 $827万
 $17,372/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -36956,7 +36956,7 @@
           <t>C | 304呎 (1房)
 $542万
 $17,822/呎
-(26年-08月-22日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
@@ -36972,7 +36972,7 @@
           <t>E | 422呎 (2房)
 $793万
 $18,791/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
@@ -36980,7 +36980,7 @@
           <t>F | 448呎 (2房)
 $819万
 $18,279/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H40" s="20" t="inlineStr">
@@ -36996,7 +36996,7 @@
           <t>H | 476呎 (2房)
 $802万
 $16,849/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -37043,7 +37043,7 @@
           <t>E | 422呎 (2房)
 $785万
 $18,604/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3785,38 +3785,30 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>15616000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>27936</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K50" s="5" t="n">
+        <v>15616000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>27936</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3825,7 +3817,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3852,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4542,7 +4534,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4604,7 +4596,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4666,7 +4658,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4852,7 +4844,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5100,7 +5092,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5286,7 +5278,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5844,7 +5836,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5906,7 +5898,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5968,7 +5960,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6092,7 +6084,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6278,7 +6270,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6340,7 +6332,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6464,7 +6456,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6774,7 +6766,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7084,7 +7076,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7146,7 +7138,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7208,7 +7200,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7332,7 +7324,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7580,7 +7572,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7704,7 +7696,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7952,7 +7944,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8262,7 +8254,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8324,7 +8316,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8572,7 +8564,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8696,7 +8688,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8758,7 +8750,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8820,7 +8812,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9192,7 +9184,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9564,7 +9556,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9812,7 +9804,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10060,7 +10052,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -11052,7 +11044,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11300,7 +11292,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -12230,7 +12222,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12540,7 +12532,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13518,7 +13510,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13642,7 +13634,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13890,7 +13882,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13952,7 +13944,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -15130,7 +15122,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15192,7 +15184,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15874,7 +15866,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15936,7 +15928,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16122,7 +16114,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16184,7 +16176,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16618,7 +16610,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17114,7 +17106,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17300,7 +17292,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17486,7 +17478,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17672,7 +17664,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17858,7 +17850,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17920,7 +17912,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18106,7 +18098,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18168,7 +18160,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18788,7 +18780,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -19098,7 +19090,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19160,7 +19152,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19284,7 +19276,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19470,7 +19462,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19842,7 +19834,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19904,7 +19896,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -21082,7 +21074,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21268,7 +21260,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21454,7 +21446,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21826,7 +21818,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21888,7 +21880,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22942,7 +22934,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -23128,7 +23120,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23748,7 +23740,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -24926,7 +24918,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -25236,7 +25228,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25856,7 +25848,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25918,7 +25910,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -26042,7 +26034,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -26104,7 +26096,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26414,7 +26406,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -27778,7 +27770,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27840,7 +27832,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -28894,7 +28886,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -29700,7 +29692,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -29762,7 +29754,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -29824,7 +29816,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -31250,7 +31242,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -31312,7 +31304,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -31746,7 +31738,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -31808,7 +31800,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -32408,7 +32400,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -32418,7 +32410,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32530,7 +32522,7 @@
           <t>B | 444呎 (2房)
 $1032万
 $23,250/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -32554,7 +32546,7 @@
           <t>E | 423呎 (2房)
 $1034万
 $24,452/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -32616,7 +32608,7 @@
           <t>A | 655呎 (3房)
 $1450万
 $22,131/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -32648,7 +32640,7 @@
           <t>E | 423呎 (2房)
 $979万
 $23,139/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -32663,7 +32655,7 @@
           <t>A | 655呎 (3房)
 $1435万
 $21,911/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -32695,7 +32687,7 @@
           <t>E | 423呎 (2房)
 $969万
 $22,910/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -32757,7 +32749,7 @@
           <t>A | 655呎 (3房)
 $1407万
 $21,479/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -32851,7 +32843,7 @@
           <t>A | 655呎 (3房)
 $1259万
 $19,226/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -32883,7 +32875,7 @@
           <t>E | 423呎 (2房)
 $931万
 $22,017/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -32906,15 +32898,15 @@
           <t>B | 444呎 (2房)
 $940万
 $21,180/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
+(26年-09月-21日)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 559呎 (3房)
-招标单位
--
-(在售)</t>
+$1562万
+$27,936/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -32992,7 +32984,7 @@
           <t>A | 655呎 (3房)
 $1296万
 $19,786/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -33039,7 +33031,7 @@
           <t>A | 655呎 (3房)
 $1233万
 $18,831/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -33063,7 +33055,7 @@
           <t>D | 676呎 (3房)
 $1690万
 $25,000/呎
-(26年-08月-23日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -33071,7 +33063,7 @@
           <t>E | 423呎 (2房)
 $830万
 $19,626/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33094,7 +33086,7 @@
           <t>B | 444呎 (2房)
 $924万
 $20,806/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -33157,7 +33149,7 @@
           <t>D | 676呎 (3房)
 $1676万
 $24,800/呎
-(26年-08月-23日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -33227,7 +33219,7 @@
           <t>A | 655呎 (3房)
 $1335万
 $20,379/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -33243,7 +33235,7 @@
           <t>C | 559呎 (3房)
 $1398万
 $25,000/呎
-(26年-08月-23日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -33251,7 +33243,7 @@
           <t>D | 676呎 (3房)
 $1663万
 $24,600/呎
-(26年-08月-23日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -33259,7 +33251,7 @@
           <t>E | 423呎 (2房)
 $811万
 $19,163/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33282,7 +33274,7 @@
           <t>B | 444呎 (2房)
 $833万
 $18,770/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -33290,7 +33282,7 @@
           <t>C | 559呎 (3房)
 $1375万
 $24,600/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -33353,7 +33345,7 @@
           <t>E | 423呎 (2房)
 $806万
 $19,050/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33400,7 +33392,7 @@
           <t>E | 423呎 (2房)
 $796万
 $18,823/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33415,7 +33407,7 @@
           <t>A | 657呎 (3房)
 $1185万
 $18,038/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -33431,7 +33423,7 @@
           <t>C | 558呎 (3房)
 $1348万
 $24,158/呎
-(26年-08月-23日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -33439,7 +33431,7 @@
           <t>D | 680呎 (3房)
 $1600万
 $23,529/呎
-(26年-08月-23日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -33447,7 +33439,7 @@
           <t>E | 422呎 (2房)
 $861万
 $20,410/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33470,7 +33462,7 @@
           <t>B | 448呎 (2房)
 $865万
 $19,315/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -33509,7 +33501,7 @@
           <t>A | 657呎 (3房)
 $1308万
 $19,915/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -33541,7 +33533,7 @@
           <t>E | 422呎 (2房)
 $842万
 $19,943/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33556,7 +33548,7 @@
           <t>A | 657呎 (3房)
 $1306万
 $19,875/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -33603,7 +33595,7 @@
           <t>A | 657呎 (3房)
 $1246万
 $18,973/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -33635,7 +33627,7 @@
           <t>E | 422呎 (2房)
 $764万
 $18,100/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33658,7 +33650,7 @@
           <t>B | 448呎 (2房)
 $819万
 $18,288/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -33666,7 +33658,7 @@
           <t>C | 558呎 (3房)
 $1252万
 $22,440/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -33674,7 +33666,7 @@
           <t>D | 680呎 (3房)
 $1448万
 $21,300/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -33697,7 +33689,7 @@
           <t>A | 657呎 (3房)
 $1301万
 $19,796/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -33791,7 +33783,7 @@
           <t>A | 657呎 (3房)
 $1293万
 $19,676/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -33823,7 +33815,7 @@
           <t>E | 422呎 (2房)
 $818万
 $19,372/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -33846,7 +33838,7 @@
           <t>B | 448呎 (2房)
 $813万
 $18,141/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -33979,7 +33971,7 @@
           <t>A | 657呎 (3房)
 $1282万
 $19,519/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -34034,7 +34026,7 @@
           <t>B | 448呎 (2房)
 $883万
 $19,712/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -34175,7 +34167,7 @@
           <t>B | 448呎 (2房)
 $868万
 $19,382/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -34222,7 +34214,7 @@
           <t>B | 448呎 (2房)
 $875万
 $19,525/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -34526,7 +34518,7 @@
           <t>A | 672呎 (3房)
 $1582万
 $23,542/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34534,7 +34526,7 @@
           <t>B | 313呎 (1房)
 $649万
 $20,748/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -34566,7 +34558,7 @@
           <t>F | 450呎 (2房)
 $996万
 $22,133/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -34582,7 +34574,7 @@
           <t>H | 473呎 (2房)
 $1058万
 $22,370/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -34771,7 +34763,7 @@
           <t>E | 418呎 (2房)
 $781万
 $18,679/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34779,7 +34771,7 @@
           <t>F | 450呎 (2房)
 $955万
 $21,229/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34810,7 +34802,7 @@
           <t>A | 672呎 (3房)
 $1409万
 $20,973/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -34818,7 +34810,7 @@
           <t>B | 313呎 (1房)
 $621万
 $19,827/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -34913,7 +34905,7 @@
           <t>E | 418呎 (2房)
 $850万
 $20,335/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -34921,7 +34913,7 @@
           <t>F | 450呎 (2房)
 $1002万
 $22,262/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -34992,7 +34984,7 @@
           <t>F | 450呎 (2房)
 $992万
 $22,042/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -35039,7 +35031,7 @@
           <t>C | 306呎 (1房)
 $596万
 $19,480/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -35063,7 +35055,7 @@
           <t>F | 450呎 (2房)
 $982万
 $21,824/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -35094,7 +35086,7 @@
           <t>A | 672呎 (3房)
 $1397万
 $20,787/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -35102,7 +35094,7 @@
           <t>B | 313呎 (1房)
 $664万
 $21,220/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -35126,7 +35118,7 @@
           <t>E | 418呎 (2房)
 $845万
 $20,215/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -35150,7 +35142,7 @@
           <t>H | 473呎 (2房)
 $953万
 $20,142/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -35197,7 +35189,7 @@
           <t>E | 418呎 (2房)
 $767万
 $18,347/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -35205,7 +35197,7 @@
           <t>F | 450呎 (2房)
 $970万
 $21,567/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -35252,7 +35244,7 @@
           <t>C | 306呎 (1房)
 $646万
 $21,127/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -35323,7 +35315,7 @@
           <t>C | 306呎 (1房)
 $617万
 $20,150/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -35339,7 +35331,7 @@
           <t>E | 418呎 (2房)
 $762万
 $18,237/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -35347,7 +35339,7 @@
           <t>F | 450呎 (2房)
 $959万
 $21,311/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -35378,7 +35370,7 @@
           <t>A | 672呎 (3房)
 $1322万
 $19,671/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -35386,7 +35378,7 @@
           <t>B | 313呎 (1房)
 $597万
 $19,073/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -35434,7 +35426,7 @@
           <t>H | 473呎 (2房)
 $1013万
 $21,410/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -35607,7 +35599,7 @@
           <t>C | 306呎 (1房)
 $609万
 $19,908/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -35631,7 +35623,7 @@
           <t>F | 450呎 (2房)
 $896万
 $19,900/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -35662,7 +35654,7 @@
           <t>A | 672呎 (3房)
 $1322万
 $19,673/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -35670,7 +35662,7 @@
           <t>B | 313呎 (1房)
 $618万
 $19,744/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -35718,7 +35710,7 @@
           <t>H | 473呎 (2房)
 $903万
 $19,087/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -35907,7 +35899,7 @@
           <t>E | 422呎 (2房)
 $746万
 $17,680/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -35931,7 +35923,7 @@
           <t>H | 476呎 (2房)
 $889万
 $18,672/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -35962,7 +35954,7 @@
           <t>C | 304呎 (1房)
 $623万
 $20,503/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -36175,7 +36167,7 @@
           <t>C | 304呎 (1房)
 $560万
 $18,424/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -36215,7 +36207,7 @@
           <t>H | 476呎 (2房)
 $945万
 $19,859/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -36230,7 +36222,7 @@
           <t>A | 672呎 (3房)
 $1336万
 $19,878/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -36333,7 +36325,7 @@
           <t>E | 422呎 (2房)
 $739万
 $17,505/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -36341,7 +36333,7 @@
           <t>F | 448呎 (2房)
 $802万
 $17,911/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -36357,7 +36349,7 @@
           <t>H | 476呎 (2房)
 $850万
 $17,863/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -36428,7 +36420,7 @@
           <t>H | 476呎 (2房)
 $845万
 $17,756/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -36514,7 +36506,7 @@
           <t>A | 672呎 (3房)
 $1374万
 $20,451/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -36522,7 +36514,7 @@
           <t>B | 313呎 (1房)
 $565万
 $18,051/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -36783,7 +36775,7 @@
           <t>H | 476呎 (2房)
 $818万
 $17,179/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -36798,7 +36790,7 @@
           <t>A | 672呎 (3房)
 $1235万
 $18,375/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -36806,7 +36798,7 @@
           <t>B | 313呎 (1房)
 $611万
 $19,534/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -36814,7 +36806,7 @@
           <t>C | 304呎 (1房)
 $592万
 $19,487/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
@@ -37011,7 +37003,7 @@
           <t>A | 672呎 (3房)
 $1249万
 $18,588/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -37019,7 +37011,7 @@
           <t>B | 313呎 (1房)
 $602万
 $19,224/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -37082,7 +37074,7 @@
           <t>A | 672呎 (3房)
 $1199万
 $17,847/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -37090,7 +37082,7 @@
           <t>B | 313呎 (1房)
 $591万
 $18,879/呎
-(26年-08月-29日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20330,7 +20330,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25786,7 +25786,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -28266,7 +28266,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28762,7 +28762,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28824,7 +28824,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -30808,7 +30808,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -31862,7 +31862,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -32569,7 +32569,7 @@
           <t>B | 444呎 (2房)
 $1020万
 $22,975/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -32593,7 +32593,7 @@
           <t>E | 423呎 (2房)
 $944万
 $22,322/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -32616,7 +32616,7 @@
           <t>B | 444呎 (2房)
 $929万
 $20,932/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -32710,7 +32710,7 @@
           <t>B | 444呎 (2房)
 $890万
 $20,043/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -32757,7 +32757,7 @@
           <t>B | 444呎 (2房)
 $965万
 $21,734/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -32804,7 +32804,7 @@
           <t>B | 444呎 (2房)
 $872万
 $19,649/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -32820,7 +32820,7 @@
           <t>D | 676呎 (3房)
 $1724万
 $25,500/呎
-(26年-08月-30日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -32914,7 +32914,7 @@
           <t>D | 676呎 (3房)
 $1710万
 $25,300/呎
-(26年-08月-31日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -32945,7 +32945,7 @@
           <t>B | 444呎 (2房)
 $935万
 $21,054/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -32961,7 +32961,7 @@
           <t>D | 676呎 (3房)
 $1704万
 $25,200/呎
-(26年-09月-02日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -32992,7 +32992,7 @@
           <t>B | 444呎 (2房)
 $848万
 $19,110/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -33133,7 +33133,7 @@
           <t>B | 444呎 (2房)
 $841万
 $18,941/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -33180,7 +33180,7 @@
           <t>B | 444呎 (2房)
 $878万
 $19,784/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -33321,7 +33321,7 @@
           <t>B | 444呎 (2房)
 $833万
 $18,770/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -33368,7 +33368,7 @@
           <t>B | 444呎 (2房)
 $819万
 $18,437/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -33509,7 +33509,7 @@
           <t>B | 448呎 (2房)
 $824万
 $18,400/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -33517,7 +33517,7 @@
           <t>C | 558呎 (3房)
 $1300万
 $23,301/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -33525,7 +33525,7 @@
           <t>D | 680呎 (3房)
 $1544万
 $22,700/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -33556,7 +33556,7 @@
           <t>B | 448呎 (2房)
 $823万
 $18,362/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -33564,7 +33564,7 @@
           <t>C | 558呎 (3房)
 $1283万
 $23,000/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -33572,7 +33572,7 @@
           <t>D | 680呎 (3房)
 $1503万
 $22,100/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -33697,7 +33697,7 @@
           <t>B | 448呎 (2房)
 $819万
 $18,288/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -33705,7 +33705,7 @@
           <t>C | 558呎 (3房)
 $1233万
 $22,100/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -33713,7 +33713,7 @@
           <t>D | 680呎 (3房)
 $1535万
 $22,576/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -33744,7 +33744,7 @@
           <t>B | 448呎 (2房)
 $816万
 $18,214/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -33885,7 +33885,7 @@
           <t>B | 448呎 (2房)
 $811万
 $18,107/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -33932,7 +33932,7 @@
           <t>B | 448呎 (2房)
 $877万
 $19,576/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -34073,7 +34073,7 @@
           <t>B | 448呎 (2房)
 $883万
 $19,712/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -34120,7 +34120,7 @@
           <t>B | 448呎 (2房)
 $803万
 $17,926/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -34261,7 +34261,7 @@
           <t>B | 410呎 (2房)
 $1017万
 $24,800/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -34269,7 +34269,7 @@
           <t>C | 521呎 (3房)
 $1246万
 $23,916/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
@@ -34277,7 +34277,7 @@
           <t>D | 643呎 (3房)
 $1286万
 $20,000/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -34534,7 +34534,7 @@
           <t>C | 306呎 (1房)
 $646万
 $21,111/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -34550,7 +34550,7 @@
           <t>E | 418呎 (2房)
 $859万
 $20,555/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -34589,7 +34589,7 @@
           <t>A | 672呎 (3房)
 $1485万
 $22,101/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -34597,7 +34597,7 @@
           <t>B | 313呎 (1房)
 $711万
 $22,725/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -34605,7 +34605,7 @@
           <t>C | 306呎 (1房)
 $638万
 $20,863/呎
-(26年-08月-29日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -34621,7 +34621,7 @@
           <t>E | 418呎 (2房)
 $830万
 $19,859/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -34629,7 +34629,7 @@
           <t>F | 450呎 (2房)
 $1065万
 $23,671/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -34645,7 +34645,7 @@
           <t>H | 473呎 (2房)
 $1132万
 $23,926/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -34660,7 +34660,7 @@
           <t>A | 672呎 (3房)
 $1452万
 $21,600/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -34668,7 +34668,7 @@
           <t>B | 313呎 (1房)
 $693万
 $22,150/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -34676,7 +34676,7 @@
           <t>C | 306呎 (1房)
 $681万
 $22,268/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34716,7 +34716,7 @@
           <t>H | 473呎 (2房)
 $1001万
 $21,167/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -34818,7 +34818,7 @@
           <t>C | 306呎 (1房)
 $668万
 $21,830/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -34858,7 +34858,7 @@
           <t>H | 473呎 (2房)
 $1005万
 $21,245/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -34873,7 +34873,7 @@
           <t>A | 672呎 (3房)
 $1405万
 $20,912/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -34881,7 +34881,7 @@
           <t>B | 313呎 (1房)
 $673万
 $21,498/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -34889,7 +34889,7 @@
           <t>C | 306呎 (1房)
 $618万
 $20,203/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -34929,7 +34929,7 @@
           <t>H | 473呎 (2房)
 $995万
 $21,036/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -34944,7 +34944,7 @@
           <t>A | 672呎 (3房)
 $1523万
 $22,663/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -35000,7 +35000,7 @@
           <t>H | 473呎 (2房)
 $962万
 $20,342/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -35157,7 +35157,7 @@
           <t>A | 672呎 (3房)
 $1389万
 $20,668/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -35165,7 +35165,7 @@
           <t>B | 313呎 (1房)
 $632万
 $20,176/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -35213,7 +35213,7 @@
           <t>H | 473呎 (2房)
 $941万
 $19,903/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -35228,7 +35228,7 @@
           <t>A | 672呎 (3房)
 $1385万
 $20,612/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -35236,7 +35236,7 @@
           <t>B | 313呎 (1房)
 $601万
 $19,188/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -35284,7 +35284,7 @@
           <t>H | 473呎 (2房)
 $1025万
 $21,666/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
           <t>A | 672呎 (3房)
 $1334万
 $19,850/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -35449,7 +35449,7 @@
           <t>B | 313呎 (1房)
 $595万
 $19,016/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -35497,7 +35497,7 @@
           <t>H | 473呎 (2房)
 $1007万
 $21,281/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -35512,7 +35512,7 @@
           <t>A | 672呎 (3房)
 $1456万
 $21,674/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -35520,7 +35520,7 @@
           <t>B | 313呎 (1房)
 $593万
 $18,958/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -35568,7 +35568,7 @@
           <t>H | 473呎 (2房)
 $1001万
 $21,154/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -35725,7 +35725,7 @@
           <t>A | 672呎 (3房)
 $1448万
 $21,546/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -35796,7 +35796,7 @@
           <t>A | 672呎 (3房)
 $1377万
 $20,485/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -35852,7 +35852,7 @@
           <t>H | 473呎 (2房)
 $977万
 $20,655/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -35938,7 +35938,7 @@
           <t>A | 672呎 (3房)
 $1296万
 $19,281/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -36009,7 +36009,7 @@
           <t>A | 672呎 (3房)
 $1290万
 $19,204/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -36025,7 +36025,7 @@
           <t>C | 304呎 (1房)
 $568万
 $18,668/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -36088,7 +36088,7 @@
           <t>B | 313呎 (1房)
 $575万
 $18,380/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -36230,7 +36230,7 @@
           <t>B | 313呎 (1房)
 $626万
 $20,010/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -36364,7 +36364,7 @@
           <t>A | 672呎 (3房)
 $1265万
 $18,823/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -36372,7 +36372,7 @@
           <t>B | 313呎 (1房)
 $568万
 $18,160/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -36380,7 +36380,7 @@
           <t>C | 304呎 (1房)
 $548万
 $18,039/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -36577,7 +36577,7 @@
           <t>A | 672呎 (3房)
 $1250万
 $18,598/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -36585,7 +36585,7 @@
           <t>B | 313呎 (1房)
 $617万
 $19,712/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -36648,7 +36648,7 @@
           <t>A | 672呎 (3房)
 $1363万
 $20,287/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -36656,7 +36656,7 @@
           <t>B | 313呎 (1房)
 $588万
 $18,799/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -36861,7 +36861,7 @@
           <t>A | 672呎 (3房)
 $1352万
 $20,125/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -36869,7 +36869,7 @@
           <t>B | 313呎 (1房)
 $558万
 $17,834/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -36932,7 +36932,7 @@
           <t>A | 672呎 (3房)
 $1342万
 $19,964/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -36940,7 +36940,7 @@
           <t>B | 313呎 (1房)
 $608万
 $19,419/呎
-(26年-08月-29日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -37201,7 +37201,7 @@
           <t>H | 437呎 (2房)
 $1197万
 $27,381/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -966,7 +966,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -2125,38 +2125,30 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>17440800</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>25800</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K24" s="5" t="n">
+        <v>17440800</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>25800</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2165,7 +2157,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2262,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2456,7 +2448,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -3410,7 +3402,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3542,7 +3534,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -4100,7 +4092,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4410,7 +4402,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4720,7 +4712,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4782,7 +4774,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -6022,7 +6014,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6580,7 +6572,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -7262,7 +7254,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -8378,7 +8370,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8440,7 +8432,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8502,7 +8494,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9370,7 +9362,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9742,7 +9734,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9928,7 +9920,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9990,7 +9982,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10238,7 +10230,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10300,7 +10292,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10548,7 +10540,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10610,7 +10602,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10982,7 +10974,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11168,7 +11160,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11478,7 +11470,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11540,7 +11532,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12098,7 +12090,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12160,7 +12152,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12408,7 +12400,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12470,7 +12462,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12656,7 +12648,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13106,7 +13098,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13168,7 +13160,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13572,7 +13564,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13758,7 +13750,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14068,7 +14060,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14254,7 +14246,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14564,7 +14556,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14750,7 +14742,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14998,7 +14990,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15308,7 +15300,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15370,7 +15362,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15432,7 +15424,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15556,7 +15548,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15742,7 +15734,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16052,7 +16044,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16238,7 +16230,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16734,7 +16726,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16858,7 +16850,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16982,7 +16974,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17354,7 +17346,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17416,7 +17408,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17540,7 +17532,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17726,7 +17718,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18036,7 +18028,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18222,7 +18214,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18532,7 +18524,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18718,7 +18710,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18966,7 +18958,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19338,7 +19330,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19400,7 +19392,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19524,7 +19516,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19710,7 +19702,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20020,7 +20012,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20206,7 +20198,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20516,7 +20508,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20950,7 +20942,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21322,7 +21314,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21384,7 +21376,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21508,7 +21500,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21694,7 +21686,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -22190,7 +22182,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22500,7 +22492,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22686,7 +22678,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22810,7 +22802,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23244,7 +23236,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23368,7 +23360,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23492,7 +23484,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23678,7 +23670,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23802,7 +23794,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -24298,7 +24290,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24484,7 +24476,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24670,7 +24662,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24856,7 +24848,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25290,7 +25282,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25352,7 +25344,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25476,7 +25468,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25662,7 +25654,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25972,7 +25964,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -26158,7 +26150,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26220,7 +26212,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26282,7 +26274,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26344,7 +26336,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26654,7 +26646,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -27212,7 +27204,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27274,7 +27266,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27336,7 +27328,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27460,7 +27452,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27646,7 +27638,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -28142,7 +28134,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28452,7 +28444,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28638,7 +28630,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -29196,7 +29188,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29320,7 +29312,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -29444,7 +29436,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -29630,7 +29622,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -29940,7 +29932,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -30188,7 +30180,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -30932,7 +30924,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -31118,7 +31110,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -31428,7 +31420,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -31614,7 +31606,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -31924,7 +31916,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -31986,7 +31978,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -32048,7 +32040,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -32110,7 +32102,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -32172,7 +32164,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -32234,7 +32226,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -32296,7 +32288,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -32400,7 +32392,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -32410,7 +32402,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32467,7 +32459,7 @@
           <t>A | 655呎 (3房)
 $1919万
 $29,300/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -32475,7 +32467,7 @@
           <t>B | 444呎 (2房)
 $1205万
 $27,133/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -32514,7 +32506,7 @@
           <t>A | 655呎 (3房)
 $1474万
 $22,500/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -32561,7 +32553,7 @@
           <t>A | 655呎 (3房)
 $1454万
 $22,200/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -32663,7 +32655,7 @@
           <t>B | 444呎 (2房)
 $899万
 $20,243/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -32674,12 +32666,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 676呎 (3房)
-招标单位
--
-(在售)</t>
+$1744万
+$25,800/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -32726,7 +32718,7 @@
           <t>D | 676呎 (3房)
 $1737万
 $25,700/呎
-(26年-09月-11日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -32851,7 +32843,7 @@
           <t>B | 444呎 (2房)
 $864万
 $19,453/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -32867,7 +32859,7 @@
           <t>D | 676呎 (3房)
 $1866万
 $27,609/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -32953,7 +32945,7 @@
           <t>C | 559呎 (3房)
 $1431万
 $25,600/呎
-(26年-09月-10日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -33000,7 +32992,7 @@
           <t>C | 559呎 (3房)
 $1425万
 $25,500/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -33039,7 +33031,7 @@
           <t>B | 444呎 (2房)
 $927万
 $20,869/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -33047,7 +33039,7 @@
           <t>C | 559呎 (3房)
 $1420万
 $25,400/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -33227,7 +33219,7 @@
           <t>B | 444呎 (2房)
 $836万
 $18,827/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -33329,7 +33321,7 @@
           <t>C | 559呎 (3房)
 $1477万
 $26,415/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -33415,7 +33407,7 @@
           <t>B | 448呎 (2房)
 $867万
 $19,350/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -33603,7 +33595,7 @@
           <t>B | 448呎 (2房)
 $821万
 $18,326/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -33611,7 +33603,7 @@
           <t>C | 558呎 (3房)
 $1269万
 $22,741/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -33619,7 +33611,7 @@
           <t>D | 680呎 (3房)
 $1482万
 $21,800/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -33752,7 +33744,7 @@
           <t>C | 558呎 (3房)
 $1324万
 $23,722/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -33791,7 +33783,7 @@
           <t>B | 448呎 (2房)
 $814万
 $18,179/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -33846,7 +33838,7 @@
           <t>C | 558呎 (3房)
 $1196万
 $21,443/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -33854,7 +33846,7 @@
           <t>D | 680呎 (3房)
 $1397万
 $20,546/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -33893,7 +33885,7 @@
           <t>C | 558呎 (3房)
 $1179万
 $21,122/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -33901,7 +33893,7 @@
           <t>D | 680呎 (3房)
 $1376万
 $20,237/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -33940,7 +33932,7 @@
           <t>C | 558呎 (3房)
 $1167万
 $20,910/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -33948,7 +33940,7 @@
           <t>D | 680呎 (3房)
 $1362万
 $20,034/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -33979,7 +33971,7 @@
           <t>B | 448呎 (2房)
 $798万
 $17,819/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -34042,7 +34034,7 @@
           <t>D | 680呎 (3房)
 $1328万
 $19,535/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -34081,7 +34073,7 @@
           <t>C | 558呎 (3房)
 $1126万
 $20,185/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -34089,7 +34081,7 @@
           <t>D | 680呎 (3房)
 $1328万
 $19,535/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -34175,7 +34167,7 @@
           <t>C | 558呎 (3房)
 $1110万
 $19,884/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
@@ -34183,7 +34175,7 @@
           <t>D | 680呎 (3房)
 $1308万
 $19,243/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -34222,7 +34214,7 @@
           <t>C | 558呎 (3房)
 $1209万
 $21,665/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
@@ -34230,7 +34222,7 @@
           <t>D | 680呎 (3房)
 $1426万
 $20,969/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -34285,7 +34277,7 @@
           <t>E | 383呎 (2房)
 $996万
 $26,000/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -34479,7 +34471,7 @@
           <t>E | 418呎 (2房)
 $978万
 $23,400/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -34487,7 +34479,7 @@
           <t>F | 450呎 (2房)
 $1215万
 $27,000/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -34542,7 +34534,7 @@
           <t>D | 307呎 (1房)
 $669万
 $21,801/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -34566,7 +34558,7 @@
           <t>G | 408呎 (2房)
 $929万
 $22,777/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -34613,7 +34605,7 @@
           <t>D | 307呎 (1房)
 $661万
 $21,541/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -34637,7 +34629,7 @@
           <t>G | 408呎 (2房)
 $908万
 $22,243/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -34684,7 +34676,7 @@
           <t>D | 307呎 (1房)
 $645万
 $20,997/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -34708,7 +34700,7 @@
           <t>G | 408呎 (2房)
 $879万
 $21,554/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -34731,7 +34723,7 @@
           <t>A | 672呎 (3房)
 $1431万
 $21,301/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34739,7 +34731,7 @@
           <t>B | 313呎 (1房)
 $627万
 $20,026/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34747,7 +34739,7 @@
           <t>C | 306呎 (1房)
 $616万
 $20,131/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34787,7 +34779,7 @@
           <t>H | 473呎 (2房)
 $991万
 $20,958/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -34826,7 +34818,7 @@
           <t>D | 307呎 (1房)
 $662万
 $21,564/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34850,7 +34842,7 @@
           <t>G | 408呎 (2房)
 $862万
 $21,130/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34897,7 +34889,7 @@
           <t>D | 307呎 (1房)
 $626万
 $20,378/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -34921,7 +34913,7 @@
           <t>G | 408呎 (2房)
 $854万
 $20,922/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -34952,7 +34944,7 @@
           <t>B | 313呎 (1房)
 $608万
 $19,435/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -34968,7 +34960,7 @@
           <t>D | 307呎 (1房)
 $620万
 $20,179/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -35015,7 +35007,7 @@
           <t>A | 672呎 (3房)
 $1398万
 $20,801/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -35023,7 +35015,7 @@
           <t>B | 313呎 (1房)
 $606万
 $19,374/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -35071,7 +35063,7 @@
           <t>H | 473呎 (2房)
 $953万
 $20,142/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -35110,7 +35102,7 @@
           <t>D | 307呎 (1房)
 $618万
 $20,117/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -35134,7 +35126,7 @@
           <t>G | 408呎 (2房)
 $916万
 $22,461/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -35181,7 +35173,7 @@
           <t>D | 307呎 (1房)
 $672万
 $21,902/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -35205,7 +35197,7 @@
           <t>G | 408呎 (2房)
 $906万
 $22,194/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -35252,7 +35244,7 @@
           <t>D | 307呎 (1房)
 $612万
 $19,922/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -35276,7 +35268,7 @@
           <t>G | 408呎 (2房)
 $822万
 $20,145/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -35299,7 +35291,7 @@
           <t>A | 672呎 (3房)
 $1380万
 $20,539/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -35307,7 +35299,7 @@
           <t>B | 313呎 (1房)
 $599万
 $19,131/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -35355,7 +35347,7 @@
           <t>H | 473呎 (2房)
 $930万
 $19,666/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -35394,7 +35386,7 @@
           <t>D | 307呎 (1房)
 $608万
 $19,805/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -35418,7 +35410,7 @@
           <t>G | 408呎 (2房)
 $812万
 $19,904/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -35465,7 +35457,7 @@
           <t>D | 307呎 (1房)
 $606万
 $19,743/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -35489,7 +35481,7 @@
           <t>G | 408呎 (2房)
 $807万
 $19,787/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -35560,7 +35552,7 @@
           <t>G | 408呎 (2房)
 $802万
 $19,667/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -35583,7 +35575,7 @@
           <t>A | 672呎 (3房)
 $1452万
 $21,610/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -35591,7 +35583,7 @@
           <t>B | 313呎 (1房)
 $592万
 $18,904/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -35639,7 +35631,7 @@
           <t>H | 473呎 (2房)
 $995万
 $21,030/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -35678,7 +35670,7 @@
           <t>D | 307呎 (1房)
 $601万
 $19,564/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -35702,7 +35694,7 @@
           <t>G | 408呎 (2房)
 $870万
 $21,311/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -35749,7 +35741,7 @@
           <t>D | 307呎 (1房)
 $629万
 $20,495/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -35804,7 +35796,7 @@
           <t>B | 313呎 (1房)
 $579万
 $18,511/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -35820,7 +35812,7 @@
           <t>D | 307呎 (1房)
 $597万
 $19,450/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -35844,7 +35836,7 @@
           <t>G | 408呎 (2房)
 $784万
 $19,228/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -35867,7 +35859,7 @@
           <t>A | 672呎 (3房)
 $1425万
 $21,202/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -35883,7 +35875,7 @@
           <t>C | 304呎 (1房)
 $571万
 $18,776/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -35946,7 +35938,7 @@
           <t>B | 313呎 (1房)
 $634万
 $20,252/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -35962,7 +35954,7 @@
           <t>D | 308呎 (1房)
 $648万
 $21,023/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -35986,7 +35978,7 @@
           <t>G | 408呎 (2房)
 $834万
 $20,431/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -36017,7 +36009,7 @@
           <t>B | 313呎 (1房)
 $577万
 $18,435/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -36080,7 +36072,7 @@
           <t>A | 672呎 (3房)
 $1392万
 $20,720/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -36104,7 +36096,7 @@
           <t>D | 308呎 (1房)
 $588万
 $19,081/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -36128,7 +36120,7 @@
           <t>G | 408呎 (2房)
 $757万
 $18,544/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -36151,7 +36143,7 @@
           <t>A | 672呎 (3房)
 $1280万
 $19,051/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -36159,7 +36151,7 @@
           <t>B | 313呎 (1房)
 $621万
 $19,853/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -36246,7 +36238,7 @@
           <t>D | 308呎 (1房)
 $584万
 $18,968/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -36270,7 +36262,7 @@
           <t>G | 408呎 (2房)
 $824万
 $20,186/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -36293,7 +36285,7 @@
           <t>A | 672呎 (3房)
 $1275万
 $18,975/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -36301,7 +36293,7 @@
           <t>B | 313呎 (1房)
 $626万
 $20,010/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -36309,7 +36301,7 @@
           <t>C | 304呎 (1房)
 $612万
 $20,118/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -36317,7 +36309,7 @@
           <t>D | 308呎 (1房)
 $584万
 $18,968/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -36341,7 +36333,7 @@
           <t>G | 408呎 (2房)
 $770万
 $18,870/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -36388,7 +36380,7 @@
           <t>D | 308呎 (1房)
 $636万
 $20,649/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -36435,7 +36427,7 @@
           <t>A | 672呎 (3房)
 $1260万
 $18,747/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -36443,7 +36435,7 @@
           <t>B | 313呎 (1房)
 $614万
 $19,613/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -36451,7 +36443,7 @@
           <t>C | 304呎 (1房)
 $547万
 $17,987/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -36530,7 +36522,7 @@
           <t>D | 308呎 (1房)
 $577万
 $18,740/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -36554,7 +36546,7 @@
           <t>G | 408呎 (2房)
 $814万
 $19,946/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -36601,7 +36593,7 @@
           <t>D | 308呎 (1房)
 $576万
 $18,685/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -36672,7 +36664,7 @@
           <t>D | 308呎 (1房)
 $574万
 $18,630/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -36696,7 +36688,7 @@
           <t>G | 408呎 (2房)
 $809万
 $19,826/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
@@ -36719,7 +36711,7 @@
           <t>A | 672呎 (3房)
 $1240万
 $18,449/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -36735,7 +36727,7 @@
           <t>C | 304呎 (1房)
 $541万
 $17,789/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -36814,7 +36806,7 @@
           <t>D | 308呎 (1房)
 $625万
 $20,279/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -36838,7 +36830,7 @@
           <t>G | 408呎 (2房)
 $804万
 $19,708/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
@@ -36877,7 +36869,7 @@
           <t>C | 304呎 (1房)
 $599万
 $19,701/呎
-(26年-08月-29日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -36909,7 +36901,7 @@
           <t>G | 408呎 (2房)
 $769万
 $18,853/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I39" s="20" t="inlineStr">
@@ -37027,7 +37019,7 @@
           <t>D | 308呎 (1房)
 $561万
 $18,224/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -37051,7 +37043,7 @@
           <t>G | 408呎 (2房)
 $797万
 $19,532/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I41" s="20" t="inlineStr">
@@ -37098,7 +37090,7 @@
           <t>D | 308呎 (1房)
 $554万
 $17,984/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -37122,7 +37114,7 @@
           <t>G | 408呎 (2房)
 $726万
 $17,789/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I42" s="20" t="inlineStr">
@@ -37145,7 +37137,7 @@
           <t>A | 634呎 (3房)
 $1744万
 $27,500/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -37153,7 +37145,7 @@
           <t>B | 276呎 (1房)
 $675万
 $24,457/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -37161,7 +37153,7 @@
           <t>C | 267呎 (1房)
 $624万
 $23,371/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
@@ -37169,7 +37161,7 @@
           <t>D | 270呎 (1房)
 $610万
 $22,607/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -37177,7 +37169,7 @@
           <t>E | 383呎 (2房)
 $895万
 $23,371/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="G43" s="20" t="inlineStr">
@@ -37185,7 +37177,7 @@
           <t>F | 411呎 (2房)
 $904万
 $22,000/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="H43" s="20" t="inlineStr">
@@ -37193,7 +37185,7 @@
           <t>G | 373呎 (2房)
 $821万
 $22,000/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -15052,7 +15052,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24972,7 +24972,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25158,7 +25158,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -28940,7 +28940,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -29126,7 +29126,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -30118,7 +30118,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -30614,7 +30614,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -32765,7 +32765,7 @@
           <t>D | 676呎 (3房)
 $1731万
 $25,600/呎
-(26年-09月-11日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -33000,7 +33000,7 @@
           <t>D | 676呎 (3房)
 $1844万
 $27,284/呎
-(26年-09月-03日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -33086,7 +33086,7 @@
           <t>C | 559呎 (3房)
 $1414万
 $25,300/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -33752,7 +33752,7 @@
           <t>D | 680呎 (3房)
 $1411万
 $20,750/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -33791,7 +33791,7 @@
           <t>C | 558呎 (3房)
 $1317万
 $23,604/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -33799,7 +33799,7 @@
           <t>D | 680呎 (3房)
 $1538万
 $22,613/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -33979,7 +33979,7 @@
           <t>C | 558呎 (3房)
 $1149万
 $20,597/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -33987,7 +33987,7 @@
           <t>D | 680呎 (3房)
 $1356万
 $19,934/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -34026,7 +34026,7 @@
           <t>C | 558呎 (3房)
 $1126万
 $20,185/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
@@ -34120,7 +34120,7 @@
           <t>C | 558呎 (3房)
 $1168万
 $20,935/呎
-(26年-09月-05日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
@@ -34128,7 +34128,7 @@
           <t>D | 680呎 (3房)
 $1315万
 $19,340/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -34747,7 +34747,7 @@
           <t>D | 307呎 (1房)
 $638万
 $20,788/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34771,7 +34771,7 @@
           <t>G | 408呎 (2房)
 $871万
 $21,341/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34984,7 +34984,7 @@
           <t>G | 408呎 (2房)
 $845万
 $20,713/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -35031,7 +35031,7 @@
           <t>D | 307呎 (1房)
 $618万
 $20,117/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -35055,7 +35055,7 @@
           <t>G | 408呎 (2房)
 $916万
 $22,461/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -35315,7 +35315,7 @@
           <t>D | 307呎 (1房)
 $610万
 $19,860/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -35339,7 +35339,7 @@
           <t>G | 408呎 (2房)
 $817万
 $20,022/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -35528,7 +35528,7 @@
           <t>D | 307呎 (1房)
 $604万
 $19,684/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -35599,7 +35599,7 @@
           <t>D | 307呎 (1房)
 $617万
 $20,091/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -35623,7 +35623,7 @@
           <t>G | 408呎 (2房)
 $874万
 $21,412/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -35725,7 +35725,7 @@
           <t>B | 313呎 (1房)
 $590万
 $18,847/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -35765,7 +35765,7 @@
           <t>G | 408呎 (2房)
 $870万
 $21,311/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -35773,7 +35773,7 @@
           <t>H | 473呎 (2房)
 $1077万
 $22,763/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -35867,7 +35867,7 @@
           <t>B | 313呎 (1房)
 $580万
 $18,546/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -35883,7 +35883,7 @@
           <t>D | 308呎 (1房)
 $593万
 $19,256/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -35907,7 +35907,7 @@
           <t>G | 408呎 (2房)
 $777万
 $19,034/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -36025,7 +36025,7 @@
           <t>D | 308呎 (1房)
 $590万
 $19,140/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -36049,7 +36049,7 @@
           <t>G | 408呎 (2房)
 $759万
 $18,598/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -36167,7 +36167,7 @@
           <t>D | 308呎 (1房)
 $586万
 $19,023/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -36191,7 +36191,7 @@
           <t>G | 408呎 (2房)
 $754万
 $18,488/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -36404,7 +36404,7 @@
           <t>G | 408呎 (2房)
 $748万
 $18,324/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -36451,7 +36451,7 @@
           <t>D | 308呎 (1房)
 $579万
 $18,799/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -36475,7 +36475,7 @@
           <t>G | 408呎 (2房)
 $745万
 $18,267/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -36617,7 +36617,7 @@
           <t>G | 408呎 (2房)
 $741万
 $18,157/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -36719,7 +36719,7 @@
           <t>B | 313呎 (1房)
 $587万
 $18,741/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -36735,7 +36735,7 @@
           <t>D | 308呎 (1房)
 $572万
 $18,575/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -36759,7 +36759,7 @@
           <t>G | 408呎 (2房)
 $736万
 $18,049/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
@@ -36877,7 +36877,7 @@
           <t>D | 308呎 (1房)
 $625万
 $20,279/呎
-(26年-09月-05日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -36948,7 +36948,7 @@
           <t>D | 308呎 (1房)
 $621万
 $20,159/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -36972,7 +36972,7 @@
           <t>G | 408呎 (2房)
 $799万
 $19,591/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I40" s="20" t="inlineStr">

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -4526,14 +4526,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>12960000</v>
+        <v>12371000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>19786</v>
+        <v>18887</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>12960000</v>
+        <v>12371000</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>19786</v>
+        <v>18887</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -5518,14 +5518,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>8155000</v>
+        <v>8932000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>19279</v>
+        <v>21116</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>8155000</v>
+        <v>8932000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>19279</v>
+        <v>21116</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -6138,14 +6138,14 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>8058000</v>
+        <v>8825000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>19050</v>
+        <v>20863</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>8058000</v>
+        <v>8825000</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>19050</v>
+        <v>20863</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -13936,14 +13936,14 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
-        <v>15820000</v>
+        <v>15188000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>23542</v>
+        <v>22601</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -13951,10 +13951,10 @@
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>15820000</v>
+        <v>15188000</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>23542</v>
+        <v>22601</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -14804,14 +14804,14 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
-        <v>6814000</v>
+        <v>6222000</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>22268</v>
+        <v>20333</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -14819,10 +14819,10 @@
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>6814000</v>
+        <v>6222000</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>22268</v>
+        <v>20333</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
@@ -25034,14 +25034,14 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
-        <v>8431000</v>
+        <v>8048000</v>
       </c>
       <c r="I392" s="5" t="n">
-        <v>18819</v>
+        <v>17964</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
@@ -25049,10 +25049,10 @@
         </is>
       </c>
       <c r="K392" s="5" t="n">
-        <v>8431000</v>
+        <v>8048000</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>18819</v>
+        <v>17964</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -26584,14 +26584,14 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
-        <v>8058000</v>
+        <v>7357000</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>19095</v>
+        <v>17434</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
@@ -26599,10 +26599,10 @@
         </is>
       </c>
       <c r="K417" s="5" t="n">
-        <v>8058000</v>
+        <v>7357000</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>19095</v>
+        <v>17434</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -29250,14 +29250,14 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
-        <v>5866000</v>
+        <v>5599000</v>
       </c>
       <c r="I460" s="5" t="n">
-        <v>18741</v>
+        <v>17888</v>
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
@@ -29265,10 +29265,10 @@
         </is>
       </c>
       <c r="K460" s="5" t="n">
-        <v>5866000</v>
+        <v>5599000</v>
       </c>
       <c r="L460" s="5" t="n">
-        <v>18741</v>
+        <v>17888</v>
       </c>
       <c r="M460" s="3" t="inlineStr">
         <is>
@@ -30490,14 +30490,14 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
-        <v>8189000</v>
+        <v>7655000</v>
       </c>
       <c r="I480" s="5" t="n">
-        <v>18279</v>
+        <v>17087</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
@@ -30505,10 +30505,10 @@
         </is>
       </c>
       <c r="K480" s="5" t="n">
-        <v>8189000</v>
+        <v>7655000</v>
       </c>
       <c r="L480" s="5" t="n">
-        <v>18279</v>
+        <v>17087</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
@@ -31172,14 +31172,14 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
-        <v>5492000</v>
+        <v>5365000</v>
       </c>
       <c r="I491" s="5" t="n">
-        <v>18066</v>
+        <v>17648</v>
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
@@ -31187,10 +31187,10 @@
         </is>
       </c>
       <c r="K491" s="5" t="n">
-        <v>5492000</v>
+        <v>5365000</v>
       </c>
       <c r="L491" s="5" t="n">
-        <v>18066</v>
+        <v>17648</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
@@ -32974,9 +32974,9 @@
       <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 655呎 (3房)
-$1296万
-$19,786/呎
-(26年-09月-18日)</t>
+$1237万
+$18,887/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -33194,9 +33194,9 @@
       <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
-$816万
-$19,279/呎
-(26年-09月-15日)</t>
+$893万
+$21,116/呎
+(26年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -33288,9 +33288,9 @@
       <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
-$806万
-$19,050/呎
-(26年-09月-14日)</t>
+$882万
+$20,863/呎
+(26年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -34508,9 +34508,9 @@
       <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 672呎 (3房)
-$1582万
-$23,542/呎
-(26年-09月-21日)</t>
+$1519万
+$22,601/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34666,9 +34666,9 @@
       <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 306呎 (1房)
-$681万
-$22,268/呎
-(26年-09月-23日)</t>
+$622万
+$20,333/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -36181,9 +36181,9 @@
       <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$843万
-$18,819/呎
-(26年-09月-16日)</t>
+$805万
+$17,964/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -36386,9 +36386,9 @@
       <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$806万
-$19,095/呎
-(26年-09月-15日)</t>
+$736万
+$17,434/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -36717,9 +36717,9 @@
       <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
-$587万
-$18,741/呎
-(26年-09月-29日)</t>
+$560万
+$17,888/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -36962,9 +36962,9 @@
       <c r="G40" s="20" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
-$819万
-$18,279/呎
-(26年-09月-15日)</t>
+$766万
+$17,087/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="H40" s="20" t="inlineStr">
@@ -37009,9 +37009,9 @@
       <c r="D41" s="20" t="inlineStr">
         <is>
           <t>C | 304呎 (1房)
-$549万
-$18,066/呎
-(26年-09月-14日)</t>
+$536万
+$17,648/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -32898,7 +32898,7 @@
           <t>C | 559呎 (3房)
 $1562万
 $27,936/呎
-(26年-09月-18日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">

--- a/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
+++ b/九龙-深水埗-叡璟I/叡璟I_销控明细表.xlsx
@@ -1618,14 +1618,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>10201000</v>
+        <v>9314000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>22975</v>
+        <v>20977</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>10201000</v>
+        <v>9314000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>22975</v>
+        <v>20977</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -9114,14 +9114,14 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>8193000</v>
+        <v>8388000</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>18288</v>
+        <v>18723</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="K136" s="5" t="n">
-        <v>8193000</v>
+        <v>8388000</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>18288</v>
+        <v>18723</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -11098,14 +11098,14 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>7054000</v>
+        <v>7734000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>16716</v>
+        <v>18327</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11113,10 +11113,10 @@
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>7054000</v>
+        <v>7734000</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>16716</v>
+        <v>18327</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -12214,14 +12214,14 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>8683000</v>
+        <v>7920000</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>19382</v>
+        <v>17679</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12229,10 +12229,10 @@
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>8683000</v>
+        <v>7920000</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>19382</v>
+        <v>17679</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -15734,14 +15734,14 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>6620000</v>
+        <v>6319000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>21564</v>
+        <v>20583</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -15749,10 +15749,10 @@
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>6620000</v>
+        <v>6319000</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>21564</v>
+        <v>20583</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -31730,14 +31730,14 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
-        <v>5909000</v>
+        <v>5395000</v>
       </c>
       <c r="I500" s="5" t="n">
-        <v>18879</v>
+        <v>17236</v>
       </c>
       <c r="J500" s="3" t="inlineStr">
         <is>
@@ -31745,10 +31745,10 @@
         </is>
       </c>
       <c r="K500" s="5" t="n">
-        <v>5909000</v>
+        <v>5395000</v>
       </c>
       <c r="L500" s="5" t="n">
-        <v>18879</v>
+        <v>17236</v>
       </c>
       <c r="M500" s="3" t="inlineStr">
         <is>
@@ -32559,9 +32559,9 @@
       <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 444呎 (2房)
-$1020万
-$22,975/呎
-(26年-09月-22日)</t>
+$931万
+$20,977/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -32671,7 +32671,7 @@
           <t>D | 676呎 (3房)
 $1744万
 $25,800/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -33687,9 +33687,9 @@
       <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$819万
-$18,288/呎
-(26年-09月-22日)</t>
+$839万
+$18,723/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -34040,9 +34040,9 @@
       <c r="F38" s="20" t="inlineStr">
         <is>
           <t>E | 422呎 (2房)
-$705万
-$16,716/呎
-(26年-09月-14日)</t>
+$773万
+$18,327/呎
+(26年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -34157,9 +34157,9 @@
       <c r="C41" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$868万
-$19,382/呎
-(26年-09月-21日)</t>
+$792万
+$17,679/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -34816,9 +34816,9 @@
       <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
-$662万
-$21,564/呎
-(26年-09月-28日)</t>
+$632万
+$20,583/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -37072,9 +37072,9 @@
       <c r="C42" s="20" t="inlineStr">
         <is>
           <t>B | 313呎 (1房)
-$591万
-$18,879/呎
-(26年-09月-21日)</t>
+$540万
+$17,236/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
